--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-18T23:52:42+00:00</t>
+    <t>2023-01-19T14:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T15:14:06+00:00</t>
+    <t>2023-01-25T17:01:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-25T17:01:00+00:00</t>
+    <t>2023-01-27T16:08:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T16:08:13+00:00</t>
+    <t>2023-01-27T21:59:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T21:59:50+00:00</t>
+    <t>2023-01-27T22:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-27T22:08:27+00:00</t>
+    <t>2023-01-31T04:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:34:49+00:00</t>
+    <t>2023-01-31T04:42:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-01-31T04:42:38+00:00</t>
+    <t>2023-01-31T18:46:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T12:10:18+00:00</t>
+    <t>2023-02-07T22:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-07T22:15:28+00:00</t>
+    <t>2023-02-08T07:55:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T07:55:54+00:00</t>
+    <t>2023-02-09T15:16:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T15:16:32+00:00</t>
+    <t>2023-02-09T17:43:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T17:43:27+00:00</t>
+    <t>2023-02-09T21:16:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-09T21:16:20+00:00</t>
+    <t>2023-02-10T06:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T06:44:21+00:00</t>
+    <t>2023-02-10T12:56:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T12:56:00+00:00</t>
+    <t>2023-02-10T14:37:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T14:37:40+00:00</t>
+    <t>2023-02-10T15:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T15:20:03+00:00</t>
+    <t>2023-02-10T23:42:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-10T23:42:05+00:00</t>
+    <t>2023-02-13T12:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T12:09:55+00:00</t>
+    <t>2023-02-13T14:15:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:15:11+00:00</t>
+    <t>2023-02-13T14:19:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T14:19:18+00:00</t>
+    <t>2023-02-13T18:35:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:35:48+00:00</t>
+    <t>2023-02-13T18:37:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:37:08+00:00</t>
+    <t>2023-02-13T18:51:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T18:51:39+00:00</t>
+    <t>2023-02-13T20:10:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-13T20:10:13+00:00</t>
+    <t>2023-02-14T12:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T12:04:08+00:00</t>
+    <t>2023-02-14T14:41:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:41:39+00:00</t>
+    <t>2023-02-14T14:58:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T14:58:50+00:00</t>
+    <t>2023-02-14T15:00:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T15:00:34+00:00</t>
+    <t>2023-02-14T18:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T18:30:52+00:00</t>
+    <t>2023-02-14T21:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>83</v>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-14T21:42:45+00:00</t>
+    <t>2023-02-15T05:04:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T05:04:04+00:00</t>
+    <t>2023-02-15T13:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T13:37:26+00:00</t>
+    <t>2023-02-15T14:04:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T14:04:38+00:00</t>
+    <t>2023-02-15T16:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:11:45+00:00</t>
+    <t>2023-02-15T16:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:17:51+00:00</t>
+    <t>2023-02-15T16:20:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:20:01+00:00</t>
+    <t>2023-02-15T16:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T16:22:21+00:00</t>
+    <t>2023-02-15T20:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-15T20:04:03+00:00</t>
+    <t>2023-02-16T23:28:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>83</v>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-16T23:28:10+00:00</t>
+    <t>2023-02-17T19:45:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-17T19:45:07+00:00</t>
+    <t>2023-02-20T03:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>83</v>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T15:31:02+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -11707,7 +11707,7 @@
       </c>
       <c r="D87" s="2"/>
       <c r="E87" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>83</v>
@@ -11931,7 +11931,7 @@
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-PractitionerLE.xlsx
+++ b/StructureDefinition-PractitionerLE.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
